--- a/AAII_Financials/Quarterly/BEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>BEN</t>
   </si>
@@ -656,344 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2358400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2294900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2327100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2343700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2064000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2111400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2251600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2211200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2122900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2152800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1991100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1986100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1969000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1927200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1967100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1939000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2031300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2081000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2224000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2181000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2172900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2076500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1995100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1705000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1161100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1311200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1389200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1347400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1476700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1433800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1411500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1527200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1558600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3233300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1615500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1616900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1613900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1600600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1560800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1611800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1456600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1436400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1468100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1447200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1304900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1349800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1388400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1368900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1314500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1353200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1220700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1166700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1202900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1190900</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1069,53 +1076,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>901800</v>
+      </c>
+      <c r="E10" s="3">
         <v>858500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>859000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>896500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>759100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>761600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>863200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>842300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>808400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>799600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>770400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>819400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>766100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>736300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,56 +1496,59 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E14" s="3">
         <v>103200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>126100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>321100</v>
       </c>
-      <c r="G14" s="3">
-        <v>101300</v>
-      </c>
       <c r="H14" s="3">
+        <v>119300</v>
+      </c>
+      <c r="I14" s="3">
         <v>222100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>169700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>429700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>90600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>183700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>118000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>96500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>32100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>63400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>208100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1544,8 +1564,8 @@
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1556,8 +1576,8 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>5</v>
@@ -1574,124 +1594,127 @@
       <c r="AG14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" s="3">
         <v>800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>500</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>500</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>300</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E15" s="3">
         <v>50600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>55100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>69200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>112200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>112500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>112600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>83800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>84000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>84600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>85800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>86500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>85400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>86000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>83200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>81500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>81800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>60400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>58300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>57900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>58000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>57900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>58200</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3">
         <v>4700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4800</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2052300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1899300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1942600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1932200</v>
       </c>
-      <c r="G17" s="3">
-        <v>1851000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1833000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1873100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1927300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1903900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1842900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1864200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1636200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1577100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1609000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1609100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1773100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1590500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1626600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1618000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1666300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1649500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1694800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1620200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1586000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1601400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>928600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>971300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1016300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1046400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1101800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1054300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1000000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1049300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1055800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2097100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1034900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1059200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1050200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1045100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>974200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1036500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>306100</v>
+      </c>
+      <c r="E18" s="3">
         <v>395600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>384500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>411500</v>
       </c>
-      <c r="G18" s="3">
-        <v>213000</v>
-      </c>
       <c r="H18" s="3">
+        <v>231000</v>
+      </c>
+      <c r="I18" s="3">
         <v>238300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>324300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>307300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>280000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>288600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>354900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>409000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>360000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>318100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>194000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>348500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>404700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>463000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>557700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>531500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>478100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>456300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>409100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>103600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>232500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>339900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>372900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>301000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>374900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>379500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>411500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>477900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>502800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1136200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>580600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>557700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>563700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>555500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>586600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>575300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-38000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-34300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-40700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-15900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-27900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-24500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-59000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-33000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-58300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-36400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-25300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>66000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-67200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-62700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>26100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>157500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>220600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>103000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>173100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>157900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>114400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>42500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-233300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>78800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>99500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>44200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>118700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-59100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>11200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-33500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>169300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>81800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>113400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>92700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>84600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>46400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>394600</v>
+      </c>
+      <c r="E21" s="3">
         <v>484200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>473900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>521400</v>
       </c>
-      <c r="G21" s="3">
-        <v>341100</v>
-      </c>
       <c r="H21" s="3">
+        <v>359100</v>
+      </c>
+      <c r="I21" s="3">
         <v>378700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>461400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>401800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>423000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>406200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>499000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>531900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>438700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>429400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>368300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>389800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>449900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>569800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>795900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>817700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>665200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>710300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>647000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>274100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>297200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>130000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>478500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>426500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>444700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>519700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>372700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>506800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>489700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1343800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>683300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>689100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>678200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>660700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>652900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>671000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E22" s="3">
         <v>19900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>27700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>34900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>33500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>27100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>28900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>22900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>25700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>29700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>18400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>22100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>20800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>10800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>12700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>12900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>12600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>13300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>370900</v>
+      </c>
+      <c r="E23" s="3">
         <v>445700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>451800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>254300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>176600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>313200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>300100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>238100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>331200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>413400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>330700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>366000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>229100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>254200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>313100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>466200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>695900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>738000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>555400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>613500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>537300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>199600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>269800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>102900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>445600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>395800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>413500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>492500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>346000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>483300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>447200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1284700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>651600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>658400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>643500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>627500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>619700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>636300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E24" s="3">
         <v>99100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>105000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>65800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>31100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>81100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>68100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>74900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>75000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>84100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>92900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>60300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>48500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>89500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>107100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>151100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>83800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>128100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>142500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>73100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>16100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>44100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>97500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>86500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>158900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>110900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>86000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>96600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>101500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>305600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>154600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>181900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>184100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>192500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>200900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>255300</v>
+      </c>
+      <c r="E26" s="3">
         <v>346600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>346800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>188500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>116700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>232100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-55700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>232000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>175300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>256300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>338400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>246600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>273100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>168800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>205700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>223600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>359100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>544800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>742800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>471600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>485400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>394800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>126500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>253700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>58800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>348100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>309300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>254600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>381600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>260000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>386700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>345700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>979100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>497000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>476500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>459400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>435000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>418800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>473000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>160400</v>
+      </c>
+      <c r="E27" s="3">
         <v>251900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>239300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>107300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>79000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>137100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>148200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-93500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>166500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>117000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>241600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>284500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>217300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>185200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>157900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>224200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>245200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>334500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>433900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>638600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>419000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>364900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>330700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>73300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>286200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>77300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>346300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>304300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>243300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>363700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>273400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>412400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>389000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>914200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>484600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>422700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>407100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>417200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>437200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3227,8 +3288,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
@@ -3245,21 +3306,21 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" s="3">
         <v>89600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>9700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-1068100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-1068900</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E32" s="3">
         <v>38000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>34300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>40700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>15900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>27900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>24500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>59000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>33000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>58300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>36400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>25300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-66000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>67200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>62700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-26100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-157500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-220600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-103000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-173100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-157900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-114400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-42500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>233300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-78800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-99500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-44200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-118700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>59100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>33500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-169300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-81800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-113400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-92700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-84600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-46400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-74400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>171500</v>
+      </c>
+      <c r="E33" s="3">
         <v>268200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>255500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>117600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>92300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>151400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>163600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-84700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>174000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>124200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>251300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>295500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>227500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>194200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>157900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>224200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>245200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>334500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>433900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>638600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>419000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>364900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>330700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>73300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>286200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>77300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>346300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>304300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>243300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>363700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>273400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>502000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>398700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-153900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-584300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>422700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>407100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>417200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>437200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>171500</v>
+      </c>
+      <c r="E35" s="3">
         <v>268200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>255500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>117600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>92300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>151400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>163600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-84700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>174000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>124200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>251300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>295500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>227500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>194200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>157900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>224200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>245200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>334500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>433900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>638600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>419000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>364900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>330700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>73300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>286200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>77300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>346300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>304300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>243300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>363700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>273400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>502000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>398700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-153900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-584300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>422700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>407100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>417200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>437200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2670300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2571500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2672100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3088100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3253900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2754000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2808000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3309500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3378500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3300200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3327400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3686400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3728600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3471300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4502200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4782500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4478700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5014700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4544300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4647200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4361100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4364700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4419500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3989800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6975900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6035800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5976300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5957600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5757600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5946000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6658900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6910600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6654200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8726500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8970400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>8749700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>8786200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>8776100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>8454800</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>8483300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1566900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1426200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1445600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1541700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1723200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1453200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1393800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1479100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1570500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1449600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1469600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1348400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1341900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1300800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1291800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1264800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1414800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1370700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1434700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1428200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1361100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1294900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1230100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1318900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>927800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>675200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>787500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>839000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>850200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>841000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>805600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>847900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>946900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>899000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1098500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1001900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>978600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1023500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>930000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>794300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16625800</v>
+      </c>
+      <c r="E45" s="3">
         <v>14807700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13285200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12764600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12123800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12644700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12734500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12134300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12364800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11973200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9915300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10353200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10298000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9228600</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20863000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18805400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17402900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17394400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17100900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16851900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16936300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16922900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17313800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16723000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14712300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15388000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15368500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14000700</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,374 +5053,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2706900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2569700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2439000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2374000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2620400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2229400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2392500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2338400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2224500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2377700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2317300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2222000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2249100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2378000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10781400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9549400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9133800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8533000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8004800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7330400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6598000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5341600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4577600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5378500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3409300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3753900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4044900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3859700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3973100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3655100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3426100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3535900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4840600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5108300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5062700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4861000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4828700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4535900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>3968900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>3930000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1638800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1666600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1681000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1713400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1747400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1767800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1772800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1769700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1749100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1795200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1600700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1206400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1237100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1203900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1235600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1207800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1245900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1142300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1178900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1218400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1227800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1266000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1324600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1348600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>963700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>975200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>967200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>683700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>684800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>576600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>541300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>535000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>522400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>517700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>516600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>517200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>508800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>509800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>512500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>523200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10315700</v>
+      </c>
+      <c r="E49" s="3">
         <v>10387000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10446000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10372000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10651900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10741900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10871200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11013500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11466300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11530200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10836300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10906000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11007200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11077600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11097500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10860700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10984500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9440100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9508900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9167900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9268100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9326200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9382600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9415000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3094800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3018600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3032200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2994500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3013400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3027900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2326200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2333400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2352900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2242300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2235100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2227700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2228000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2224000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2200400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2211300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,53 +5678,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>718600</v>
+      </c>
+      <c r="E52" s="3">
         <v>681100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>580200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>431200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>431600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>398800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>417200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>343900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>501200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>481600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>399200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>266900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>372700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>425500</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36243000</v>
+      </c>
+      <c r="E54" s="3">
         <v>34109800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32549100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32368300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32552200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31989800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32390000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32464500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33254900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32907700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29865800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30121200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30234600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29085700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29335100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>28060600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27596000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25832900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24995100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24168400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23129100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21869800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21229600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21684500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15617000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>14666200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15001800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>14532200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14463300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14239000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13950600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14383500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15528000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>17690000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>18074400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>17534000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>17476200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>17210100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>16210300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>16098800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,157 +6145,161 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>632700</v>
+      </c>
+      <c r="E57" s="3">
         <v>585400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>597600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>615400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>765800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>585400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>585000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>551500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>532200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>573700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>533900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>530000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>563500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>501200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1199200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1113100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>993100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1159000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1151300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1037300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>767800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>759800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>609100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1038100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>341900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>315500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>253000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>304400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>260400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>255000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>209400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>226900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>253800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>262500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>380900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>291500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>275000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>259300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>214800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>233300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>195600</v>
       </c>
       <c r="E58" s="3">
         <v>450000</v>
       </c>
       <c r="F58" s="3">
+        <v>450000</v>
+      </c>
+      <c r="G58" s="3">
         <v>599200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>166900</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>400000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -6173,22 +6307,22 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>254700</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -6208,38 +6342,38 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>685600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>613800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>99400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>50800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>31800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>32800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>32700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>32600</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1244700</v>
+      </c>
+      <c r="E59" s="3">
         <v>991800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>875000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1270500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1328100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>675300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1442700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1267700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1156500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1269200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1147000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>863200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1192000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>989900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2262300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2515900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2310800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2069200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2264000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2391300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2177300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2290300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2411800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2531500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1630500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1485200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1700300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1464500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1448400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1396700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1430000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1568100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1712200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3233700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1646800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>509900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>473500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>390400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>498100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>462000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2964200</v>
+        <v>3803100</v>
       </c>
       <c r="E60" s="3">
+        <v>3414200</v>
+      </c>
+      <c r="F60" s="3">
         <v>3127800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4245400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3875100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2562600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3159500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4020500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3380400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3255500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2844800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3313000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3216700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2697400</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,252 +6643,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3430400</v>
+        <v>3376500</v>
       </c>
       <c r="E61" s="3">
+        <v>2980400</v>
+      </c>
+      <c r="F61" s="3">
         <v>3088600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2763400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3668500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3660500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3722000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3345400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4010600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4024200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3912300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3265900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3853500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3887200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9535000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8834100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8878700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8488100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7572300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7070400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6655400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5246000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5130300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5817700</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>697200</v>
       </c>
       <c r="AB61" s="3">
         <v>697200</v>
       </c>
       <c r="AC61" s="3">
+        <v>697200</v>
+      </c>
+      <c r="AD61" s="3">
         <v>697000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>696900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>697000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>697900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>697700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>695900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>729800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1078800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1095500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1097600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1427800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1680200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1734500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2083400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14321600</v>
+      </c>
+      <c r="E62" s="3">
         <v>12762700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11622100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10909100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10309700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10377900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9889000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10248900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10541400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10354300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8999500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9518000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9124400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8758400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>258200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>347800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>290900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>252300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>218500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>311700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>321200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>289800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>298600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>305300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>77200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>126200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>132800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>120100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>118900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>130200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>132600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>126500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>128000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>129900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>125300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>170600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>156500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>159800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>151700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>161500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21842300</v>
+      </c>
+      <c r="E66" s="3">
         <v>19494500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18156700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18179500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18117300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16811800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17050300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17899700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18353500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18072100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16149700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16547300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16645300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15682600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17668800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16586000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16052300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14292200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13442200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12945000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12253900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11306400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10828700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11570000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5502800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4762800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4920200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4625700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4552300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4355200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4205200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4484300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5664500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7631600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6316300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4914000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5076200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5016500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4245500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4163000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11520600</v>
+      </c>
+      <c r="E72" s="3">
         <v>11560900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11540100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11516000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11610300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11730000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11919100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11927600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12321300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12265400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12402400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12376600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12360700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12260100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12112600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12045600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11997500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11891300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11892200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11550800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11151000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10861500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10665100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10472600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10514800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10330000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10408000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10288200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10241500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10219500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10087900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10217900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10153500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10263900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>11969500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>12849300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>12665200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>12510600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>12326000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>12226200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11738200</v>
+      </c>
+      <c r="E76" s="3">
         <v>12123800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12134900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12077800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12203900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12346000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12462100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12508100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12870200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12861100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12001600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11916900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11948100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11831800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11666300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11474600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11543700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11540700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11552900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11223400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10875200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10563400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10400900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10114500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10114200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9903400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10081600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9906500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9911000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9883800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9745400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9899200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9863500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10058400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11758100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12620000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12400000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>12193600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11964800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>11935800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>171500</v>
+      </c>
+      <c r="E81" s="3">
         <v>268200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>255500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>117600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>92300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>151400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>163600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-84700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>174000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>124200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>251300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>295500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>227500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>194200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>157900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>224200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>245200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>334500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>433900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>638600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>419000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>364900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>330700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>73300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>286200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>77300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>346300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>304300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>243300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>363700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>273400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>502000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>398700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-153900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-584300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>422700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>407100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>417200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>437200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E83" s="3">
         <v>30500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>29000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>27800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>27000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>108300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>108500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>107900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>80700</v>
       </c>
       <c r="U83" s="3">
         <v>80700</v>
       </c>
       <c r="V83" s="3">
+        <v>80700</v>
+      </c>
+      <c r="W83" s="3">
         <v>65600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>84100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>80900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>80000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>96200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>36100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>23400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>26800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>26000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>25600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>20300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>17700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>38300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>20900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>18000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>21800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>20600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>19900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>581200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-255100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1282100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-50100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-145200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>558200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>528400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>136600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-251900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>764500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>654300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-256300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>866400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>819800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>104100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>166400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>506100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>193000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>255100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>291200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>380700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>561600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>109300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>31700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>32300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-274900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>178200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>266000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>721200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>611500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>897000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>320400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>177100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>344000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>168100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>446200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>562300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-15000</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3">
         <v>-31200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-37500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-71800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-69800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-34700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-44400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-18400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-47800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-130400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-46500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-43700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-36200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1660600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1358700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-317200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-441400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-880700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-364100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-656500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1201000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-811900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-273200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-137600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-332100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1056900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1178700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1042600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-649300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1528600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-422700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-728600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-679900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1163000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-251200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-521800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3512200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>263000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>35700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-68300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-274600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-635100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-99100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-17600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-91300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-181500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-58600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-12900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>132500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-58400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>100200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>176200</v>
+      </c>
+      <c r="E96" s="3">
         <v>176400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>170200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>171100</v>
-      </c>
-      <c r="G96" s="3">
-        <v>173200</v>
       </c>
       <c r="H96" s="3">
         <v>173200</v>
       </c>
       <c r="I96" s="3">
+        <v>173200</v>
+      </c>
+      <c r="J96" s="3">
         <v>166200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>167100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>167900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>165700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>155700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>152500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>153000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>153400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-148400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-146000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-146600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-147400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-143100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-141100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-141800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-142000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-134800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-134100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-133900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-134600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-130600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-131100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-132100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-133100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-122300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-122000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1755900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-239000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-111700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-111800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-112700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-113300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-103400</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-104100</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1274500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1491100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>487400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>88500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>292400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>87900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>909200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>274300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>391100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-159000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-385900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>505800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1027900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>958900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>95800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>213300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>808600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>467300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>487200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>212100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>370000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>960800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>155400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>643100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>261500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>360800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-266700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-396100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-445000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2552200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-764500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-51100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-225200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-369000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>4100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-365900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-425000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E101" s="3">
         <v>15800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-50000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>30800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>25700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-31700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>59700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-40500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>59700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-40500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-19600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-27300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>10200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>27700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>21200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>11000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>25900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-25500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-11300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-40300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>25800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>10000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>24500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>44300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>16600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-50400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>191900</v>
+      </c>
+      <c r="E102" s="3">
         <v>84200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-89100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-383100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>417900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-106000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-763800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>297200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>244700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-522800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>109000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-223600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-280300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>303800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-536000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>470400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-102900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>286100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-242800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>146000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>468100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3018400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>940100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>59500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-188400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-712900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-251700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>256400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2072300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>220700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-36500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>10100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>321300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-28500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>241200</v>
       </c>
     </row>
